--- a/customer_service_forms/007_promotion_dispute_complaint_form--customer_service_forms.xlsx
+++ b/customer_service_forms/007_promotion_dispute_complaint_form--customer_service_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'open',_'value':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Open', 'value': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'resolved',_'value':_'resolved'}</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Resolved', 'value': 'Resolved'}</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Closed', 'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'approved',_'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Approved', 'value': 'approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'denied',_'value':_'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Denied', 'value': 'denied'}</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress', 'value': 'in_progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
